--- a/data/trans_dic/IP1012-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1012-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen ceguera o problemas de visión</t>
+          <t>Menores que padecen ceguera o problemas de visión (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,68</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,55</t>
+          <t>0,15; 1,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,99</t>
+          <t>0,47; 4,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,97</t>
+          <t>0,35; 2,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,59</t>
+          <t>0,89; 8,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,06</t>
+          <t>0,45; 4,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,88</t>
+          <t>0,1; 0,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,94</t>
+          <t>0,1; 0,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,58</t>
+          <t>0,39; 1,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,46</t>
+          <t>0,33; 1,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,97</t>
+          <t>0,09; 1,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,98</t>
+          <t>0,32; 1,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,97</t>
+          <t>0,26; 0,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,49</t>
+          <t>0,05; 0,45</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen ceguera o problemas de visión (tasa de respuesta: 99,78%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4231</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4252</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4049</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4828</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4620</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3089</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4195</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3250</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3545</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3075</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3212</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3132</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3830</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4300</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2547</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4330</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3097</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1658</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2314</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2658</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4147</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5223</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3051</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4774</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>636; 6944</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3079</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2364</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3232</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3717</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>654; 6906</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3533</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1017; 7521</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2157</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2890</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3694</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>642; 5928</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>656; 7315</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2318</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>7698</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>7583</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>634; 6236</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>657; 6095</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2651; 11331</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2330; 10486</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>651; 7473</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4220; 13982</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3660; 13759</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>647; 6262</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1012-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1012-Clase-trans_dic.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 3,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,22 +703,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
     </row>
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,61</t>
+          <t>0,15; 1,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,94</t>
+          <t>0,47; 4,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,6</t>
+          <t>0,32; 2,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,19</t>
+          <t>0,88; 8,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,97</t>
+          <t>0,5; 4,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,98</t>
+          <t>0,1; 0,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,9</t>
+          <t>0,1; 1,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,32 +1353,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,66</t>
+          <t>0,41; 1,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,47</t>
+          <t>0,32; 1,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,05</t>
+          <t>0,11; 0,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,06</t>
+          <t>0,31; 1,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,99</t>
+          <t>0,27; 1,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,45</t>
+          <t>0,05; 0,49</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4231</t>
+          <t>0; 2970</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4252</t>
+          <t>0; 4115</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4049</t>
+          <t>0; 3381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1664,22 +1664,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4828</t>
+          <t>0; 4163</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4620</t>
+          <t>0; 4527</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3089</t>
+          <t>0; 3391</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4195</t>
+          <t>0; 4676</t>
         </is>
       </c>
     </row>
@@ -1817,32 +1817,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3250</t>
+          <t>0; 3257</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3545</t>
+          <t>0; 3902</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3075</t>
+          <t>0; 3785</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3212</t>
+          <t>0; 3416</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3132</t>
+          <t>0; 3125</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3830</t>
+          <t>0; 4527</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4300</t>
+          <t>0; 5903</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2547</t>
+          <t>0; 3437</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4330</t>
+          <t>0; 4331</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3097</t>
+          <t>0; 3086</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2658</t>
+          <t>0; 3704</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2143,32 +2143,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4147</t>
+          <t>0; 4653</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5223</t>
+          <t>0; 6485</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3051</t>
+          <t>0; 3324</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4774</t>
+          <t>0; 4882</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>636; 6944</t>
+          <t>631; 6385</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3079</t>
+          <t>0; 3106</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3232</t>
+          <t>0; 3238</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3717</t>
+          <t>0; 4959</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>654; 6906</t>
+          <t>651; 6829</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3533</t>
+          <t>0; 3433</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1017; 7521</t>
+          <t>918; 7936</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3694</t>
+          <t>0; 3727</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>642; 5928</t>
+          <t>640; 5952</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>656; 7315</t>
+          <t>736; 6602</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>634; 6236</t>
+          <t>633; 5725</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>657; 6095</t>
+          <t>655; 7193</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2632,32 +2632,32 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2651; 11331</t>
+          <t>2798; 11538</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2330; 10486</t>
+          <t>2284; 10648</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>651; 7473</t>
+          <t>756; 6431</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4220; 13982</t>
+          <t>4073; 13333</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3660; 13759</t>
+          <t>3678; 13879</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>647; 6262</t>
+          <t>714; 6813</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1012-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1012-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,48</t>
+          <t>0,15; 1,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
     </row>
@@ -1065,27 +1065,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,47; 4,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,88</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,75</t>
+          <t>0,32; 2,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0,98%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>0,88; 8,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,22</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,48</t>
+          <t>0,5; 5,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,42 +1338,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,9</t>
+          <t>0,38; 1,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,07</t>
+          <t>0,28; 1,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,1; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,69</t>
+          <t>0,1; 0,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,49</t>
+          <t>0,1; 0,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,01</t>
+          <t>0,3; 0,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,0</t>
+          <t>0,27; 0,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1538,27 +1538,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>746</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2970</t>
+          <t>0; 4039</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4115</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>0; 3833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3756</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4163</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4527</t>
+          <t>0; 4125</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3391</t>
+          <t>0; 3723</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4676</t>
+          <t>0; 4865</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>624</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>759</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3809</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3155</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3830</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3257</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3902</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3785</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3416</t>
+          <t>0; 3241</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3125</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4527</t>
+          <t>0; 4135</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>866</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>619</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4332</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3132</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5903</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3437</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4331</t>
+          <t>0; 5172</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3086</t>
+          <t>0; 3127</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1658</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1658</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5278</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3704</t>
+          <t>0; 6295</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3121</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4653</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6485</t>
+          <t>0; 3484</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3324</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4882</t>
+          <t>0; 4592</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>631; 6385</t>
+          <t>632; 6724</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3106</t>
+          <t>0; 3563</t>
         </is>
       </c>
     </row>
@@ -2185,27 +2185,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2364</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>915</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2364</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3238</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4959</t>
+          <t>652; 6972</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3205</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>651; 6829</t>
+          <t>0; 4300</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3433</t>
+          <t>0; 3194</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>918; 7936</t>
+          <t>915; 8597</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2348,22 +2348,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2401,22 +2401,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2157</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>733</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3727</t>
+          <t>641; 6220</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>640; 5952</t>
+          <t>0; 4344</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>736; 6602</t>
+          <t>732; 7444</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2318</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>5266</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>633; 5725</t>
+          <t>2611; 10809</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>655; 7193</t>
+          <t>2023; 10398</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>713; 6898</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2798; 11538</t>
+          <t>632; 5606</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2284; 10648</t>
+          <t>656; 6322</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>756; 6431</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4073; 13333</t>
+          <t>4008; 12992</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3678; 13879</t>
+          <t>3748; 13424</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>714; 6813</t>
+          <t>712; 6832</t>
         </is>
       </c>
     </row>
